--- a/Practical3/Excel Sheets/Task 3.xlsx
+++ b/Practical3/Excel Sheets/Task 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/bhwkau001_myuct_ac_za/Documents/Y3S2/Embedded2/Prac 3/Excel Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{EFFA0397-7381-4C73-A7F9-A6B9FFF7D433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B954A7-D847-44BA-880F-58246B1C3C90}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{EFFA0397-7381-4C73-A7F9-A6B9FFF7D433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ABBACB0-C711-4AD8-9ECD-C16E023F89B2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E3951509-9FF2-4361-990B-B96AA9D57802}"/>
   </bookViews>
@@ -423,6 +423,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -441,72 +442,72 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3629</v>
+        <v>2698</v>
       </c>
       <c r="B2">
-        <v>4183093</v>
+        <v>429384</v>
       </c>
       <c r="C2">
-        <v>435589876</v>
+        <v>323771630</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>10945</v>
+        <v>4400</v>
       </c>
       <c r="B3">
-        <v>7281324</v>
+        <v>669829</v>
       </c>
       <c r="C3">
-        <v>757877525</v>
+        <v>527974622</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>21414</v>
+        <v>6307</v>
       </c>
       <c r="B4">
-        <v>11567405</v>
+        <v>966024</v>
       </c>
       <c r="C4">
-        <v>1136269068</v>
+        <v>756908681</v>
       </c>
       <c r="D4">
-        <v>46</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>42626</v>
+        <v>8482</v>
       </c>
       <c r="B5">
-        <v>24101281</v>
+        <v>1314999</v>
       </c>
       <c r="C5">
-        <v>2425413935</v>
+        <v>1018072347</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>78810</v>
+        <v>10805</v>
       </c>
       <c r="B6">
-        <v>40659164</v>
+        <v>1715812</v>
       </c>
       <c r="C6">
-        <v>4221973931</v>
+        <v>1296791070</v>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>6064</v>
       </c>
     </row>
   </sheetData>
